--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6506.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6506.xlsx
@@ -1785,6 +1785,9 @@
       <c r="F21" t="n">
         <v>0.172</v>
       </c>
+      <c r="G21" t="n">
+        <v>0.57</v>
+      </c>
       <c r="H21" t="n">
         <v>0.675</v>
       </c>
@@ -1803,12 +1806,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C1HEX@HEX, D@BORE, L18@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C1HEX@HEX, D@BORE, L18@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6506-06-04 (PARTcommunity / CADENAS, C1HEX@HEX=C4, D@BORE=AD, L18@DRIVE=L2, THDMAJ_A@DRIVE=BTHD, THDMAJ_B@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6506-06-04 (PARTcommunity / CADENAS, C1HEX@HEX=C4, D@BORE=AD, L18@DRIVE=L2, THDMAJ_A@DRIVE=BTHD, THDMAJ_B@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1842,6 +1845,9 @@
       <c r="F22" t="n">
         <v>0.484</v>
       </c>
+      <c r="G22" t="n">
+        <v>0.57</v>
+      </c>
       <c r="H22" t="n">
         <v>0.675</v>
       </c>
@@ -1860,12 +1866,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C1HEX@HEX, D@BORE, L18@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C1HEX@HEX, D@BORE, L18@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6506-06-10 (PARTcommunity / CADENAS, C1HEX@HEX=C4, D@BORE=AD, L18@DRIVE=L2, THDMAJ_A@DRIVE=BTHD, THDMAJ_B@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6506-06-10 (PARTcommunity / CADENAS, C1HEX@HEX=C4, D@BORE=AD, L18@DRIVE=L2, THDMAJ_A@DRIVE=BTHD, THDMAJ_B@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1890,6 +1896,9 @@
           <t>6506-12-08</t>
         </is>
       </c>
+      <c r="G23" t="n">
+        <v>0.91</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>6506-12-08</t>
@@ -1902,12 +1911,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1936,6 +1945,9 @@
       <c r="F24" t="n">
         <v>1.781</v>
       </c>
+      <c r="G24" t="n">
+        <v>2.2</v>
+      </c>
       <c r="H24" t="n">
         <v>2.375</v>
       </c>
@@ -1954,12 +1966,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C1HEX@HEX, D@BORE, L18@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C1HEX@HEX, D@BORE, L18@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6506-32-32 (PARTcommunity / CADENAS, C1HEX@HEX=C4, D@BORE=AD, L18@DRIVE=L2, THDMAJ_A@DRIVE=BTHD, THDMAJ_B@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6506-32-32 (PARTcommunity / CADENAS, C1HEX@HEX=C4, D@BORE=AD, L18@DRIVE=L2, THDMAJ_A@DRIVE=BTHD, THDMAJ_B@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
